--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -1673,13 +1673,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05BBDCCF-0465-4697-B228-CCB4C4B5B545}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36830D40-E15C-4A80-A6FC-C86D4291D9E0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A0C69EA-80F8-4405-876D-1E29C977A33F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E11749D0-14AE-4BAD-8E66-3B20A27856ED}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A124CB5F-8A02-4DA9-A012-E2B695FB266B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B1892E5-A7EA-4281-B15E-7DE7DB58AE51}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -1673,13 +1673,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36830D40-E15C-4A80-A6FC-C86D4291D9E0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54DF86ED-B9A9-401C-BBE1-E5BECFCA6FD5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E11749D0-14AE-4BAD-8E66-3B20A27856ED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29B52A20-4A28-47B8-B6A1-5501F7EEDC2E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B1892E5-A7EA-4281-B15E-7DE7DB58AE51}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1FEE164-42DF-40DC-B8DA-8D1DD7AA30A8}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -1673,13 +1673,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54DF86ED-B9A9-401C-BBE1-E5BECFCA6FD5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDB4EB68-3704-4F42-A820-773310EC140D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29B52A20-4A28-47B8-B6A1-5501F7EEDC2E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{367D24DD-B870-48C9-B128-810D5F1FE398}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1FEE164-42DF-40DC-B8DA-8D1DD7AA30A8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5EDA592E-FFD7-47B3-A61E-CB3DE68CED52}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -1673,13 +1673,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDB4EB68-3704-4F42-A820-773310EC140D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8539F98A-5CFB-464E-9A3F-1705022DAE8E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{367D24DD-B870-48C9-B128-810D5F1FE398}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{929C75C7-27F9-4880-8295-0F24DCBAA9AE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5EDA592E-FFD7-47B3-A61E-CB3DE68CED52}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{223219A3-36F6-451A-8D79-87B22FC9F084}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:P44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -383,6 +383,56 @@
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Sleep_h_day_Source</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>SWS_total_pct</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>SWS_total_pct_Source</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>USWS_pctTST</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>USWS_pctTST_Source</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Torpor_type</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Torpor_type_Source</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Torpor_Tb_min_C</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Torpor_Tb_min_C_Source</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Torpor_bout_max_h</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Torpor_bout_max_h_Source</t>
         </is>
       </c>
     </row>
@@ -1673,13 +1723,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8539F98A-5CFB-464E-9A3F-1705022DAE8E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12EBE9D2-2822-46CA-8211-D8165D6B2341}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{929C75C7-27F9-4880-8295-0F24DCBAA9AE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23FE0348-98AC-4EE5-9A6C-B5A8BDD2A8E4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{223219A3-36F6-451A-8D79-87B22FC9F084}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75344A5E-3601-4296-8DC1-31992446DBBD}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -1664,22 +1664,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDB4EB68-3704-4F42-A820-773310EC140D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{780175DF-47A6-4119-AC46-60D1665B1BAD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{367D24DD-B870-48C9-B128-810D5F1FE398}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A6D41ED-9CD6-4EE8-897E-B625CE486A45}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5EDA592E-FFD7-47B3-A61E-CB3DE68CED52}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C3CCAB7-5442-4049-8B6A-DC42153798D5}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -1714,22 +1714,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12EBE9D2-2822-46CA-8211-D8165D6B2341}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38FE6136-4704-4A03-A622-323F439C44A0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{23FE0348-98AC-4EE5-9A6C-B5A8BDD2A8E4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD806AA4-3B62-4765-BAAC-14244C406957}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75344A5E-3601-4296-8DC1-31992446DBBD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FCE8367-9BB7-45B6-91FF-3EA501FEE2F1}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -1723,13 +1723,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38FE6136-4704-4A03-A622-323F439C44A0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CE23C87-81A6-40F3-AEFF-7AAF9F67DA0A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD806AA4-3B62-4765-BAAC-14244C406957}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B157D9C0-8D39-401B-BD01-758556A19D11}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FCE8367-9BB7-45B6-91FF-3EA501FEE2F1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76C7D98B-B6DE-42C5-A815-C78035FBB1A5}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P44"/>
+  <dimension ref="A1:P257"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -439,291 +439,501 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Aotus trivirgatus</t>
+          <t>Acomys russatus</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aotus trivirgatus</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>16.97</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Herculano-Houzel 2015 (daily sleep)</t>
+          <t>Acomys russatus</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ateles geoffroyi</t>
+          <t>Acrobates pygmaeus</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ateles geoffroyi</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+          <t>Acrobates pygmaeus</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Blarina brevicauda</t>
+          <t>Aegotheles cristatus</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Blarina brevicauda</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>14.9</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Herculano-Houzel 2015 (daily sleep)</t>
+          <t>Aegotheles cristatus</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>22.4</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>10.7</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bos taurus</t>
+          <t>Aeronautes saxatalis</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bos taurus</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>3.19</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Herculano-Houzel 2015 (daily sleep)</t>
+          <t>Aeronautes saxatalis</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Callithrix jacchus</t>
+          <t>Aethomys namaquenesis</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Callithrix jacchus</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+          <t>Aethomys namaquenesis</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>18.9</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Callithrix sp.</t>
+          <t>Allactaga euphratica</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Callithrix sp.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>10.22</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Herculano-Houzel 2015 (daily sleep)</t>
+          <t>Allactaga euphratica</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cavia porcellus</t>
+          <t>Allactaga williamsi</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cavia porcellus</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>9.37</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Herculano-Houzel 2015 (daily sleep)</t>
+          <t>Allactaga williamsi</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cebus apella</t>
+          <t>Amazilia versicolor</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cebus apella</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>5.95</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Herculano-Houzel 2015 (daily sleep)</t>
+          <t>Amazilia versicolor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>21.8</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Chlorocebus pygerythrus</t>
+          <t>Amblysomus hottentotus</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Chlorocebus pygerythrus</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+          <t>Amblysomus hottentotus</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Chlorocebus sabaeus</t>
+          <t>Antechinomys laniger</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chlorocebus sabaeus</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+          <t>Antechinomys laniger</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Condylura cristata</t>
+          <t>Antechinus flavipes</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Condylura cristata</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>10.32</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Herculano-Houzel 2015 (daily sleep)</t>
+          <t>Antechinus flavipes</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>24.5</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dendrohyrax sp.</t>
+          <t>Antechinus stuartii</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dendrohyrax sp.</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>5.4</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Herculano-Houzel 2015 (daily sleep)</t>
+          <t>Antechinus stuartii</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Erinaceus europaeus</t>
+          <t>Aotus trivirgatus</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Erinaceus europaeus</t>
+          <t>Aotus trivirgatus</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>13.96</t>
+          <t>16.97</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -735,257 +945,367 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Erythrocebus patas</t>
+          <t>Apodemus peninsulae</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Erythrocebus patas</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+          <t>Apodemus peninsulae</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Eulemur fulvus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Eulemur fulvus</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+          <t>Apus apus</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Eulemur macaco</t>
+          <t>Archilochus alexandri</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Eulemur macaco</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+          <t>Archilochus alexandri</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>13.5</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Eulemur mongoz</t>
+          <t>Artamus cyanopterus</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Eulemur mongoz</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+          <t>Artamus cyanopterus</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Galago senegalensis</t>
+          <t>Atelerix algirus</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Galago senegalensis</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+          <t>Atelerix algirus</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>9.7</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Giraffa camelopardalis</t>
+          <t>Atelerix frontalis</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Giraffa camelopardalis</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>3.44</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Herculano-Houzel 2015 (daily sleep)</t>
+          <t>Atelerix frontalis</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Homo sapiens</t>
+          <t>Ateles geoffroyi</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Homo sapiens</t>
+          <t>Ateles geoffroyi</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>8.47</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Herculano-Houzel 2015 (daily sleep)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Loxodonta africana</t>
+          <t>Baiomys taylori</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Loxodonta africana</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Herculano-Houzel 2015 (daily sleep)</t>
+          <t>Baiomys taylori</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Macaca arctoides</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Macaca arctoides</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+          <t>Barbastella barbastellus</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Macaca fascicularis</t>
+          <t>Blarina brevicauda</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Macaca fascicularis</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+          <t>Blarina brevicauda</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>14.9</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Herculano-Houzel 2015 (daily sleep)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Macaca mulatta</t>
+          <t>Bos taurus</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Macaca mulatta</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+          <t>Bos taurus</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>8.74</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -997,34 +1317,54 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Macaca nemestrina</t>
+          <t>Burramys parvus</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Macaca nemestrina</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+          <t>Burramys parvus</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Macaca radiata</t>
+          <t>Callithrix jacchus</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Macaca radiata</t>
+          <t>Callithrix jacchus</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1035,285 +1375,385 @@
       <c r="D27" t="inlineStr">
         <is>
           <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>9.02</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Herculano-Houzel 2015 (daily sleep)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Macaca sylvanus</t>
+          <t>Callithrix sp.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Macaca sylvanus</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+          <t>Callithrix sp.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>10.22</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Herculano-Houzel 2015 (daily sleep)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mesocricetus auratus</t>
+          <t>Calomys musculinus</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mesocricetus auratus</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>14.98</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Herculano-Houzel 2015 (daily sleep)</t>
+          <t>Calomys musculinus</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Microcebus murinus</t>
+          <t>Calomys venustus</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Microcebus murinus</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+          <t>Calomys venustus</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>16.4</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Mus musculus</t>
+          <t>Calypte anna</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mus musculus</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>11.6</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Herculano-Houzel 2015 (daily sleep)</t>
+          <t>Calypte anna</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Oryctolagus cuniculus</t>
+          <t>Calypte costae</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Oryctolagus cuniculus</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>9.55</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Herculano-Houzel 2015 (daily sleep)</t>
+          <t>Calypte costae</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Pan troglodytes</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Pan troglodytes</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
+          <t>Caprimulgus europaeus</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Papio anubis</t>
+          <t>Caprimulgus guttatus</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Papio anubis</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+          <t>Caprimulgus guttatus</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>29.6</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Papio cynocephalus</t>
+          <t>Caprimulgus tristigma</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Papio cynocephalus</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>6.19</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Herculano-Houzel 2015 (daily sleep)</t>
+          <t>Caprimulgus tristigma</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Papio hamadryas</t>
+          <t>Caprimulgus vociferus</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Papio hamadryas</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+          <t>Caprimulgus vociferus</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>18.5</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Papio papio</t>
+          <t>Carollia perspicillata</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Papio papio</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+          <t>Carollia perspicillata</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Pongo pygmaeus</t>
+          <t>Cavia porcellus</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pongo pygmaeus</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+          <t>Cavia porcellus</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>9.37</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Herculano-Houzel 2015 (daily sleep)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Procavia sp.</t>
+          <t>Cebus apella</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Procavia sp.</t>
+          <t>Cebus apella</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1325,120 +1765,7966 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rattus norvegicus</t>
+          <t>Cercartetus concinnus</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Rattus norvegicus</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>12.27</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Herculano-Houzel 2015 (daily sleep)</t>
+          <t>Cercartetus concinnus</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Saimiri sciureus</t>
+          <t>Cercartetus lepidus</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Saimiri sciureus</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>9.11</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Herculano-Houzel 2015 (daily sleep)</t>
+          <t>Cercartetus lepidus</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Scalopus aquaticus</t>
+          <t>Cercartetus nanus</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Scalopus aquaticus</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>8.45</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Herculano-Houzel 2015 (daily sleep)</t>
+          <t>Cercartetus nanus</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sus scrofa</t>
+          <t>Chalinolobus gouldii</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sus scrofa</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Herculano-Houzel 2015 (daily sleep)</t>
+          <t>Chalinolobus gouldii</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>Cheirogaleus crossleyi</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Cheirogaleus crossleyi</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Cheirogaleus medius</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Cheirogaleus medius</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>1680</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Chlorocebus pygerythrus</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Chlorocebus pygerythrus</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Chlorocebus sabaeus</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Chlorocebus sabaeus</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Chordeiles acutipennis</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Chordeiles acutipennis</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>15.7</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Chordeiles minor</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Chordeiles minor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Chrysuronia oenone</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Chrysuronia oenone</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Clytolaema rubricauda</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Clytolaema rubricauda</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Colius castanotus</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Colius castanotus</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Colius colius</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Colius colius</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Colius striatus</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Colius striatus</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>18.2</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Condylura cristata</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Condylura cristata</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>10.32</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Herculano-Houzel 2015 (daily sleep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Corynorhinus rafinesquii</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Corynorhinus rafinesquii</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>13.9</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Cricetus cricetus</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Cricetus cricetus</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Crocidura flavescens</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Crocidura flavescens</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Crocidura leucodon</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Crocidura leucodon</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>18.6</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Crocidura russula</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Crocidura russula</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>17.9</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Crocidura suaveolens</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Crocidura suaveolens</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>21.6</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Cynomys leucurus</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Cynomys leucurus</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Cynomys ludovicianus</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Cynomys ludovicianus</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Cynomys parvidens</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Cynomys parvidens</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Dacelo novaeguineae</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Dacelo novaeguineae</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>28.6</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Dasykaluta rosamondae</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Dasykaluta rosamondae</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>16.4</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Dasyuroides byrnei</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Dasyuroides byrnei</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>20.4</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Dasyurus geoffroii</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Dasyurus geoffroii</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>23.1</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Dasyurus hallucatus</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Dasyurus hallucatus</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>28.4</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Dasyurus viverrinus</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Dasyurus viverrinus</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Delichon urbicum</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Delichon urbicum</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Delphinapterus leucas</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Delphinapterus leucas</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Lyamin et al. 2008 (cetacean slow-wave sleep)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>68.1</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Lyamin et al. 2008 (cetacean slow-wave sleep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Dendrohyrax sp.</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Dendrohyrax sp.</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Herculano-Houzel 2015 (daily sleep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Drepanoptila holosericea</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Drepanoptila holosericea</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>24.8</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Dromiciops gliroides</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Dromiciops gliroides</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Echinops telfairi</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Echinops telfairi</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Elephantulus edwardii</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Elephantulus edwardii</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Elephantulus myurus</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Elephantulus myurus</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Elephantulus rozeti</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Elephantulus rozeti</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>20.1</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Elephantulus rupestris</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Elephantulus rupestris</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Eliomys quercinus</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Eliomys quercinus</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Eptesicus fuscus</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Eptesicus fuscus</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Erinaceus europaeus</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Erinaceus europaeus</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>13.96</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Herculano-Houzel 2015 (daily sleep)</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Erythrocebus patas</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Erythrocebus patas</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Eugenes fulgens</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Eugenes fulgens</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Eulampis jugularis</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Eulampis jugularis</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Eulemur fulvus</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Eulemur fulvus</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Eulemur macaco</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Eulemur macaco</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Eulemur mongoz</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Eulemur mongoz</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Eupetomena macroura</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Eupetomena macroura</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Fukomys damarensis</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Fukomys damarensis</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>28.5</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Galago moholi</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Galago moholi</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>21.8</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Galago senegalensis</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Galago senegalensis</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Geogale aurita</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Geogale aurita</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Gerbillus pusillus</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Gerbillus pusillus</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>16.7</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Giraffa camelopardalis</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Giraffa camelopardalis</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Herculano-Houzel 2015 (daily sleep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Glirulus japonicus</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Glirulus japonicus</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Glis glis</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Glis glis</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Glossophaga soricina</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Glossophaga soricina</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>17.5</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Gracilinanus agilis</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Gracilinanus agilis</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Graphiurus murinus</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Graphiurus murinus</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Graphiurus ocularis</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Graphiurus ocularis</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Hipposideros terasensis</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Hipposideros terasensis</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>13.8</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>456</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Hirundapus caudacutus</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Hirundapus caudacutus</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>8.47</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Herculano-Houzel 2015 (daily sleep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Ictidomys tridecemlineatus</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Ictidomys tridecemlineatus</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>456</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Inia geoffrensis</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Inia geoffrensis</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Lyamin et al. 2008 (cetacean slow-wave sleep)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>71.9</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Lyamin et al. 2008 (cetacean slow-wave sleep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Jaculus orientalis</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Jaculus orientalis</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Lampornis clemenciae</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Lampornis clemenciae</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Lasiurus borealis</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Lasiurus borealis</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Lasiurus cinereus</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Lasiurus cinereus</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Loxodonta africana</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Loxodonta africana</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Herculano-Houzel 2015 (daily sleep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Macaca arctoides</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Macaca arctoides</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Macaca fascicularis</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Macaca fascicularis</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Macaca mulatta</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Macaca mulatta</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>8.74</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Herculano-Houzel 2015 (daily sleep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Macaca nemestrina</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Macaca nemestrina</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Macaca radiata</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Macaca radiata</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>9.02</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Herculano-Houzel 2015 (daily sleep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Macaca sylvanus</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Macaca sylvanus</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Macroglossus minimus</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Macroglossus minimus</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>21.6</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Macroscelides proboscideus</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Macroscelides proboscideus</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Manacus vitellinus</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Manacus vitellinus</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>26.8</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Marmosa microtarsus</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Marmosa microtarsus</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Marmota broweri</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Marmota broweri</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Marmota flaviventris</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Marmota flaviventris</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Marmota marmota</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Marmota marmota</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Marmota monax</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Marmota monax</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Megaloglossus woermanni</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Megaloglossus woermanni</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>26.2</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Melanotrochilus fuscus</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Melanotrochilus fuscus</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Meles meles</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Meles meles</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Mephitis mephitis</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Mephitis mephitis</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Mesocricetus auratus</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Mesocricetus auratus</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>14.98</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Herculano-Houzel 2015 (daily sleep)</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Mesocricetus brandti</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Mesocricetus brandti</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Microcebus griseorufus</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Microcebus griseorufus</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>1848</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Microcebus murinus</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Microcebus murinus</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>17.6</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Microcebus myoxinus</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Microcebus myoxinus</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>19.2</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Microcebus ravelobensis</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Microcebus ravelobensis</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Microdipodops pallidus</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Microdipodops pallidus</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Microgale dobsoni</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Microgale dobsoni</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Miniopterus schreibersii</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Miniopterus schreibersii</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Mops condylurus</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Mops condylurus</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Mus musculus</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Mus musculus</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Herculano-Houzel 2015 (daily sleep)</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Muscardinus avellanarius</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Muscardinus avellanarius</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Myotis adversus</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Myotis adversus</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Myotis lucifugus</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Myotis lucifugus</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>1152</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Myotis myotis</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Myotis myotis</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>2352</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Myotis nattereri</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Myotis nattereri</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Myotis velifer</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Myotis velifer</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Myrmecobius fasciatus</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Myrmecobius fasciatus</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>19.1</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>15.3</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Nectarinia famosa</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Nectarinia famosa</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>25.4</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Ningaui yvonnae</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Ningaui yvonnae</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>15.3</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>12.3</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Notiosorex crawfordi</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Notiosorex crawfordi</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>27.4</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Nycteris thebaica</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Nycteris thebaica</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Nyctimene albiventer</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Nyctimene albiventer</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>25.5</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Nyctophilus bifax</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Nyctophilus bifax</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Nyctophilus geoffroyi</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Nyctophilus geoffroyi</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Nyctophilus gouldi</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Nyctophilus gouldi</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Oreotrochilus estella</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Oreotrochilus estella</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Orthorhynchus cristatus</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Orthorhynchus cristatus</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>20.8</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Oryctolagus cuniculus</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Oryctolagus cuniculus</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>9.55</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Herculano-Houzel 2015 (daily sleep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Otus senegalensis</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Otus senegalensis</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Pan troglodytes</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Pan troglodytes</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Panterpe insignis</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Panterpe insignis</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Papio anubis</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Papio anubis</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Papio cynocephalus</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Papio cynocephalus</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>6.19</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Herculano-Houzel 2015 (daily sleep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Papio hamadryas</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Papio hamadryas</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Papio papio</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Papio papio</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Perognathus californicus</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Perognathus californicus</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>15.4</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Perognathus fasciatus</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Perognathus fasciatus</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Perognathus longimembris</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Perognathus longimembris</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Perognathus parvus</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Perognathus parvus</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Peromyscus boylii</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Peromyscus boylii</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Peromyscus crinitus</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Peromyscus crinitus</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Peromyscus eremicus</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Peromyscus eremicus</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Peromyscus gossypinus</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Peromyscus gossypinus</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Peromyscus leucopus</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Peromyscus leucopus</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>16.8</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Peromyscus maniculatus</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Peromyscus maniculatus</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>13.4</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>10.8</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Petaurus breviceps</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Petaurus breviceps</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>10.4</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Petromyscus collinus</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Petromyscus collinus</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Phalaenoptilus nuttallii</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Phalaenoptilus nuttallii</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Phocoena phocoena</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Phocoena phocoena</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>46.4</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Lyamin et al. 2008 (cetacean slow-wave sleep)</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>Lyamin et al. 2008 (cetacean slow-wave sleep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Phodopus sungorus</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Phodopus sungorus</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>12.3</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>13.8</t>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Phyllotis darwini</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Phyllotis darwini</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>17.5</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Pipistrellus pipistrellus</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Pipistrellus pipistrellus</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Pipistrellus subflavus</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Pipistrellus subflavus</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Planigale gilesi</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Planigale gilesi</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>15.3</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Planigale ingrami</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Planigale ingrami</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Planigale maculata</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Planigale maculata</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Planigale tenuirostris</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Planigale tenuirostris</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Podargus strigoides</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Podargus strigoides</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>29.1</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Pongo pygmaeus</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Pongo pygmaeus</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Procavia sp.</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Procavia sp.</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>5.45</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Herculano-Houzel 2015 (daily sleep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Proteles cristata</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Proteles cristata</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Pseudantechinus macdonnellensis</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Pseudantechinus macdonnellensis</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>15.9</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Rattus norvegicus</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Rattus norvegicus</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>12.27</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Herculano-Houzel 2015 (daily sleep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Reithrodontomys megalotis</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Reithrodontomys megalotis</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Rhinolophus ferrumequinum</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Rhinolophus ferrumequinum</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Rhinolophus hipposideros</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Rhinolophus hipposideros</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>2064</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Rhinopoma microphyllum</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Rhinopoma microphyllum</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Saccostomus campestris</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Saccostomus campestris</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Saimiri sciureus</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Saimiri sciureus</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Eagleman &amp; Vaughn 2021 (REM sleep)</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>9.11</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Herculano-Houzel 2015 (daily sleep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Scalopus aquaticus</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Scalopus aquaticus</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>8.45</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Herculano-Houzel 2015 (daily sleep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Scardafella inca</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Scardafella inca</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Scotophilus dinganii</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Scotophilus dinganii</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>18.5</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Scotophilus mhlanganii</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Scotophilus mhlanganii</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>17.2</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>18.5</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Selasphorus platycercus</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Selasphorus platycercus</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Selasphorus rufus</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Selasphorus rufus</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Selasphorus sasin</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Selasphorus sasin</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Setifer setosus</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Setifer setosus</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>3600</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Sminthopsis crassicaudata</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Sminthopsis crassicaudata</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>10.8</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>19.5</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Sminthopsis douglasi</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Sminthopsis douglasi</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>16.9</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Sminthopsis macroura</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Sminthopsis macroura</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>11.3</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>25.9</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Sminthopsis murina</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Sminthopsis murina</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Sminthopsis ooldea</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Sminthopsis ooldea</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Sorex sinuosus</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Sorex sinuosus</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Spermophilus armatus</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Spermophilus armatus</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>576</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Spermophilus beecheyi</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Spermophilus beecheyi</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Spermophilus beldingi</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Spermophilus beldingi</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Spermophilus citellus</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Spermophilus citellus</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>-0.7</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Spermophilus columbianus</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Spermophilus columbianus</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Spermophilus dauricus</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Spermophilus dauricus</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>-2.4</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Spermophilus elegans</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Spermophilus elegans</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Spermophilus lateralis</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Spermophilus lateralis</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Spermophilus mexicanus</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Spermophilus mexicanus</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Spermophilus parryii</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Spermophilus parryii</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>-2.9</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Spermophilus richardsonii</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Spermophilus richardsonii</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>456</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Spermophilus saturatus</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Spermophilus saturatus</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Spermophilus tereticaudus</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Spermophilus tereticaudus</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Spermophilus variegatus</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Spermophilus variegatus</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Spermophilus xanthoprymnus</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Spermophilus xanthoprymnus</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Steatomys pratensis</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Steatomys pratensis</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>16.4</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>16.9</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Sturnira lilium</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Sturnira lilium</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Suncus etruscus</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Suncus etruscus</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Sus scrofa</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Sus scrofa</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Herculano-Houzel 2015 (daily sleep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Syconycteris australis</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Syconycteris australis</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>17.2</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Tachyglossus aculeatus</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Tachyglossus aculeatus</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Tadarida aegyptiaca</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Tadarida aegyptiaca</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Tadarida brasiliensis</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Tadarida brasiliensis</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Tadarida teniotis</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Tadarida teniotis</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Tamias amoenus</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Tamias amoenus</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>-0.2</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Tamias striatus</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Tamias striatus</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Tarsipes rostratus</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Tarsipes rostratus</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>14.4</t>
+        </is>
+      </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Taxidea taxus</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Taxidea taxus</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Tenrec ecaudatus</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Tenrec ecaudatus</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>6480</t>
+        </is>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Thylamys elegans</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Thylamys elegans</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Todus mexicanus</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Todus mexicanus</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>22.4</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
           <t>Tupaia sp.</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B248" t="inlineStr">
         <is>
           <t>Tupaia sp.</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E248" t="inlineStr">
         <is>
           <t>15.84</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F248" t="inlineStr">
         <is>
           <t>Herculano-Houzel 2015 (daily sleep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Tursiops truncatus</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Tursiops truncatus</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>33.9</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Lyamin et al. 2008 (cetacean slow-wave sleep)</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>88.2</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>Lyamin et al. 2008 (cetacean slow-wave sleep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Urocolius indicus</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Urocolius indicus</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Urocolius macrourus</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Urocolius macrourus</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Ursus americanus</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Ursus americanus</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>29.4</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Ursus arctos</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Ursus arctos</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>32.5</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Vespadelus vulturnus</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Vespadelus vulturnus</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Zaedyus pichiy</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Zaedyus pichiy</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>12.5</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Zapus hudsonius</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Zapus hudsonius</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Zapus princeps</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Zapus princeps</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>HIB</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>Ruf &amp; Geiser 2015 (torpor/hibernation)</t>
         </is>
       </c>
     </row>
@@ -1723,13 +10009,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CE23C87-81A6-40F3-AEFF-7AAF9F67DA0A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07CC4497-2880-4CD8-A451-AAC6420B2E9E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B157D9C0-8D39-401B-BD01-758556A19D11}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B28E8E9C-1BE7-4EDC-9461-649D17F5AE0E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76C7D98B-B6DE-42C5-A815-C78035FBB1A5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29CD0E5D-8AD0-47D4-85DE-6094812EB035}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -10009,13 +10009,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07CC4497-2880-4CD8-A451-AAC6420B2E9E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFE8B3B5-E9B6-4BB7-B788-F967F82CFCFC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B28E8E9C-1BE7-4EDC-9461-649D17F5AE0E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{636C1AD2-0C02-40C4-9FA1-698B7C8ABDF9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29CD0E5D-8AD0-47D4-85DE-6094812EB035}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94F35977-15A0-4761-8D48-3A84EE83EDB0}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -10009,13 +10009,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFE8B3B5-E9B6-4BB7-B788-F967F82CFCFC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C2ADF0A-F70C-4A3D-B146-EC1A9ED7E38B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{636C1AD2-0C02-40C4-9FA1-698B7C8ABDF9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{244EF048-2A1F-43FA-A5A4-AE41A6D3BA74}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94F35977-15A0-4761-8D48-3A84EE83EDB0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D4BA823-A009-4548-B58F-88B3CFC3261F}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -10009,13 +10009,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C2ADF0A-F70C-4A3D-B146-EC1A9ED7E38B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74E56332-92BF-4798-AAEF-D07091D18458}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{244EF048-2A1F-43FA-A5A4-AE41A6D3BA74}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{115FCC7E-D2EC-423C-823A-778B44CCEBAD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D4BA823-A009-4548-B58F-88B3CFC3261F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9A76D7A-2E80-4FEB-9F96-FE117560FC9E}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -10009,13 +10009,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74E56332-92BF-4798-AAEF-D07091D18458}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D1F4F8D-FB6D-4B32-9467-CA7273EB3E39}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{115FCC7E-D2EC-423C-823A-778B44CCEBAD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF756ACD-61BF-4E56-8A0C-91E9296C7C39}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9A76D7A-2E80-4FEB-9F96-FE117560FC9E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D4C37AA-1BE8-43A0-A24B-C42736B5FD3B}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -10009,13 +10009,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D1F4F8D-FB6D-4B32-9467-CA7273EB3E39}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EF939B2-DC0B-4536-8CDB-C00E68EE31CF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF756ACD-61BF-4E56-8A0C-91E9296C7C39}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4C3B7F7-6889-4E17-AC0A-94EE2F6ABEF8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D4C37AA-1BE8-43A0-A24B-C42736B5FD3B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1161C4C0-FD40-4476-BC87-75B14BDCBA89}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -10009,13 +10009,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EF939B2-DC0B-4536-8CDB-C00E68EE31CF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1E5E4DF-D7BB-4A3D-A960-2A9DC01CE6AA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4C3B7F7-6889-4E17-AC0A-94EE2F6ABEF8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A0E4A0D-6AAB-4930-B488-6FFDD92FF2A7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1161C4C0-FD40-4476-BC87-75B14BDCBA89}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{563C0F45-F88B-405C-87FA-D1A17E7EAA80}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -10009,13 +10009,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1E5E4DF-D7BB-4A3D-A960-2A9DC01CE6AA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DB9F2A2-A89D-4E1F-864D-2A3091D0963E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A0E4A0D-6AAB-4930-B488-6FFDD92FF2A7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BB71489-1F71-4422-ADDC-D5BD86910189}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{563C0F45-F88B-405C-87FA-D1A17E7EAA80}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E398B34D-EAE2-4168-8EF8-AD5B13EE7E03}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -10009,13 +10009,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DB9F2A2-A89D-4E1F-864D-2A3091D0963E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DA470CB-42CB-4D46-AEA5-D97E8EC86D80}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BB71489-1F71-4422-ADDC-D5BD86910189}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF5A6532-E530-4E1C-B32E-2EE960909305}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E398B34D-EAE2-4168-8EF8-AD5B13EE7E03}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50CC0953-3399-47D3-9549-065A79AB61AA}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -10009,13 +10009,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DA470CB-42CB-4D46-AEA5-D97E8EC86D80}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADE5EF45-FA95-42CC-A07F-A50983A50151}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF5A6532-E530-4E1C-B32E-2EE960909305}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1106F04-667E-4824-A583-D85B2239D64C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50CC0953-3399-47D3-9549-065A79AB61AA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39FFA35C-8061-41F6-A702-8DD716DBFE4C}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -10009,13 +10009,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADE5EF45-FA95-42CC-A07F-A50983A50151}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83CE607B-1D96-409E-A6B2-3770DB058ECD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1106F04-667E-4824-A583-D85B2239D64C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5CB5F4D-7FE9-4577-8F6F-431E72335B95}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39FFA35C-8061-41F6-A702-8DD716DBFE4C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F404E289-14B0-4B07-92D1-ED888F6E56A1}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -10009,13 +10009,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83CE607B-1D96-409E-A6B2-3770DB058ECD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECAB1D7E-BE64-4C2F-8650-08F170C2E1AF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5CB5F4D-7FE9-4577-8F6F-431E72335B95}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD658CDD-3A2F-43AF-98D1-4D518629C206}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F404E289-14B0-4B07-92D1-ED888F6E56A1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38FAD59E-934E-41AB-ACC7-264175095588}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -10009,13 +10009,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECAB1D7E-BE64-4C2F-8650-08F170C2E1AF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5117CFBF-47B2-419D-81F5-4B91997D18E3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD658CDD-3A2F-43AF-98D1-4D518629C206}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F65ACDD2-E999-4797-A9C0-667A52C1839A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38FAD59E-934E-41AB-ACC7-264175095588}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C213E05A-C198-4BE3-A41F-27850816E3B6}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -10009,13 +10009,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5117CFBF-47B2-419D-81F5-4B91997D18E3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD8D9865-273B-4DC7-9E4F-F74B08132C01}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F65ACDD2-E999-4797-A9C0-667A52C1839A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2558326B-6AD8-49D1-978A-08A5165FA2EB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C213E05A-C198-4BE3-A41F-27850816E3B6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9E80C8-F119-4F99-88A7-6BC92C92F92E}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -10009,13 +10009,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD8D9865-273B-4DC7-9E4F-F74B08132C01}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82F32AA5-A0D1-4702-9588-9435616016FA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2558326B-6AD8-49D1-978A-08A5165FA2EB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F6ECD49-653F-45B9-9087-636351A327ED}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9E80C8-F119-4F99-88A7-6BC92C92F92E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{920386F3-669F-4EE4-8A71-06E0DE556BA6}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -10009,13 +10009,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82F32AA5-A0D1-4702-9588-9435616016FA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D5CE46A-05B0-4922-A0B3-BA0E1044AAC3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F6ECD49-653F-45B9-9087-636351A327ED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A44FBB7-75D3-4A17-A530-EF0DBE195895}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{920386F3-669F-4EE4-8A71-06E0DE556BA6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B889C3F-2A9E-4E2F-B097-BABFC0D635F7}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -10009,13 +10009,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D5CE46A-05B0-4922-A0B3-BA0E1044AAC3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13A772AB-57F6-4CC2-8152-A732D11C0C60}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A44FBB7-75D3-4A17-A530-EF0DBE195895}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7FCBF111-7A6E-45E3-9512-2A0302815631}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B889C3F-2A9E-4E2F-B097-BABFC0D635F7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5C31A2E-649F-4A08-8B9D-237EB936A57C}"/>
 </file>
--- a/____EvoM1_TraitTable/sleep.xlsx
+++ b/____EvoM1_TraitTable/sleep.xlsx
@@ -10009,13 +10009,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13A772AB-57F6-4CC2-8152-A732D11C0C60}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A6E4B2E-EA8F-45C7-97BB-9B8C649FB158}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7FCBF111-7A6E-45E3-9512-2A0302815631}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D30AC0A-5A53-42C4-A42C-E789E07419BD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5C31A2E-649F-4A08-8B9D-237EB936A57C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B117F00-9503-4607-A341-03A9EEB2713B}"/>
 </file>